--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513655_FASEFINALAFFA2_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513655_FASEFINALAFFA2_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.793100000000001</v>
+        <v>7.8566</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8017</v>
+        <v>6.0043</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9914</v>
+        <v>1.8523</v>
       </c>
       <c r="G2" t="n">
         <v>1.2306</v>
@@ -610,13 +610,13 @@
         <v>1.1684</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1204</v>
+        <v>1.1839</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3752</v>
+        <v>0.5778</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7452</v>
+        <v>0.6061</v>
       </c>
       <c r="V2" t="n">
         <v>4.2737</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2807</v>
+        <v>3.6321</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0322</v>
+        <v>1.3193</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2485</v>
+        <v>2.3128</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3601</v>
+        <v>2.6751</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5448</v>
+        <v>2.8372</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8153</v>
+        <v>-0.1621</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.3103</v>
+        <v>3.0828</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.3186</v>
+        <v>1.7371</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008399999999999999</v>
+        <v>1.3457</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0499</v>
+        <v>-0.4077</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7738</v>
+        <v>1.1001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8236</v>
+        <v>-1.5078</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9474</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9474</v>
+        <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6935</v>
+        <v>0.9559</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1213</v>
+        <v>-0.012</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.9679</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.1695</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2211</v>
+        <v>1.1695</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3841</v>
+        <v>2.1597</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8209</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5632</v>
+        <v>1.2207</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6751</v>
+        <v>-1.3601</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8372</v>
+        <v>-0.5448</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1621</v>
+        <v>-0.8153</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0828</v>
+        <v>-1.3103</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7371</v>
+        <v>-1.3186</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3457</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4077</v>
+        <v>-0.0499</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1001</v>
+        <v>0.7738</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5078</v>
+        <v>-0.8236</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1684</v>
+        <v>1.9474</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7526</v>
+        <v>1.9474</v>
       </c>
       <c r="S4" t="n">
-        <v>0.708</v>
+        <v>1.5724</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5104</v>
+        <v>1.0282</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2183</v>
+        <v>0.5443</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1695</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1695</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RUIZ CANAMERO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9254</v>
+        <v>1.2841</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5235</v>
+        <v>0.7667</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.598</v>
+        <v>0.5174</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6563</v>
+        <v>0.7605</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5658</v>
+        <v>3.1461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9095</v>
+        <v>-2.3857</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5576</v>
+        <v>1.5669</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5171</v>
+        <v>2.3118</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-0.7449</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9013</v>
+        <v>-0.8064</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0487</v>
+        <v>0.8343</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.95</v>
+        <v>-1.6407</v>
       </c>
       <c r="P6" t="n">
         <v>0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3895</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7789</v>
+        <v>1.3632</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3802</v>
+        <v>0.6931</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3553</v>
+        <v>0.1735</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0248</v>
+        <v>0.5196</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5005</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5005</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7367</v>
+        <v>0.9639</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.418</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3541</v>
+        <v>1.3819</v>
       </c>
       <c r="G7" t="n">
         <v>2.039</v>
@@ -1000,13 +1000,13 @@
         <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1144</v>
+        <v>0.1128</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3092</v>
+        <v>-0.1098</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1948</v>
+        <v>0.2226</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9932</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5631</v>
+        <v>0.7059</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2684</v>
+        <v>-0.5077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2947</v>
+        <v>1.2136</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7605</v>
+        <v>-1.8616</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1461</v>
+        <v>0.3089</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3857</v>
+        <v>-2.1705</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5669</v>
+        <v>-1.3946</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3118</v>
+        <v>-0.1872</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7449</v>
+        <v>-1.2074</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8064</v>
+        <v>-0.467</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8343</v>
+        <v>0.4961</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6407</v>
+        <v>-0.9631</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3895</v>
+        <v>0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9737</v>
+        <v>-0.3895</v>
       </c>
       <c r="R8" t="n">
         <v>1.3632</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0279</v>
+        <v>0.6523</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3249</v>
+        <v>0.0554</v>
       </c>
       <c r="U8" t="n">
-        <v>0.297</v>
+        <v>0.5969</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.9416</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3009</v>
+        <v>0.5986</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.001</v>
+        <v>2.2244</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3018</v>
+        <v>-1.6259</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1558</v>
+        <v>1.6563</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3311</v>
+        <v>2.5658</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1753</v>
+        <v>-0.9095</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7308</v>
+        <v>2.5576</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3547</v>
+        <v>2.5171</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.624</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5749</v>
+        <v>-0.9013</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0236</v>
+        <v>0.0487</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5513</v>
+        <v>-0.95</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9474</v>
+        <v>0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3105</v>
+        <v>-0.3895</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3632</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2024</v>
+        <v>0.0533</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0198</v>
+        <v>0.0563</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1825</v>
+        <v>-0.003</v>
       </c>
       <c r="V9" t="n">
-        <v>0.89</v>
+        <v>-1.5005</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3311</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1589</v>
+        <v>-0.2098</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3051</v>
+        <v>-1.943</v>
       </c>
       <c r="F10" t="n">
-        <v>1.464</v>
+        <v>1.7332</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8616</v>
+        <v>-1.1634</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3089</v>
+        <v>1.1335</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1705</v>
+        <v>-2.2969</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3946</v>
+        <v>-0.7635</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1872</v>
+        <v>1.1084</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2074</v>
+        <v>-1.8719</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.467</v>
+        <v>-0.3999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4961</v>
+        <v>0.0251</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9631</v>
+        <v>-0.4249</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9737</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3895</v>
+        <v>-1.3632</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3632</v>
+        <v>1.9474</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1053</v>
+        <v>0.3694</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.742</v>
+        <v>0.1837</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.1857</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9416</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. COSTA I VAZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5483</v>
+        <v>-0.2532</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1423</v>
+        <v>-1.4993</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5941</v>
+        <v>1.2462</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1634</v>
+        <v>0.1558</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1335</v>
+        <v>1.3311</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2969</v>
+        <v>-1.1753</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7635</v>
+        <v>0.7308</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1084</v>
+        <v>1.3547</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8719</v>
+        <v>-0.624</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3999</v>
+        <v>-0.5749</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0251</v>
+        <v>-0.0236</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4249</v>
+        <v>-0.5513</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5842000000000001</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3632</v>
+        <v>-3.3105</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9474</v>
+        <v>1.3632</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0309</v>
+        <v>0.6484</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0157</v>
+        <v>0.5215</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0466</v>
+        <v>0.1269</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2331</v>
+        <v>-1.6804</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5392</v>
+        <v>-3.231</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6938</v>
+        <v>1.5506</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1669</v>
+        <v>-1.2034</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1914</v>
+        <v>0.0303</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3583</v>
+        <v>-1.2337</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3196</v>
+        <v>-1.1535</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.6106</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4017</v>
+        <v>-0.5429</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.0499</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1093</v>
+        <v>0.6409</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9565</v>
+        <v>-0.6907</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1947</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.3895</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1947</v>
+        <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>0.408</v>
+        <v>0.2503</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1698</v>
+        <v>-0.1301</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2382</v>
+        <v>0.3805</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2795</v>
+        <v>0.0516</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2795</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.617</v>
+        <v>-2.3049</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0284</v>
+        <v>-1.6389</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4114</v>
+        <v>-0.666</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2034</v>
+        <v>-2.1669</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0303</v>
+        <v>0.1914</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2337</v>
+        <v>-2.3583</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1535</v>
+        <v>-1.3196</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6106</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5429</v>
+        <v>-1.4017</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0499</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6409</v>
+        <v>0.1093</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6907</v>
+        <v>-0.9565</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7789</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9474</v>
+        <v>-0.3895</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1684</v>
+        <v>0.1947</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6862</v>
+        <v>0.3362</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9275</v>
+        <v>0.0702</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2413</v>
+        <v>0.266</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0516</v>
+        <v>-0.2795</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0516</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.5799</v>
+        <v>-2.5878</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.0698</v>
+        <v>-4.2724</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4899</v>
+        <v>1.6847</v>
       </c>
       <c r="G14" t="n">
         <v>-1.483</v>
@@ -1546,13 +1546,13 @@
         <v>1.7526</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6491</v>
+        <v>0.3431</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9275</v>
+        <v>-0.1301</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2784</v>
+        <v>0.4732</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2795</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.6883</v>
+        <v>11.6885</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7327999999999992</v>
+        <v>-0.7328999999999986</v>
       </c>
       <c r="F15" t="n">
-        <v>12.4213</v>
+        <v>12.4215</v>
       </c>
       <c r="G15" t="n">
         <v>0.8026000000000004</v>
@@ -1597,7 +1597,7 @@
         <v>-11.3951</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1107</v>
+        <v>5.110700000000001</v>
       </c>
       <c r="K15" t="n">
         <v>7.538900000000001</v>
@@ -1609,7 +1609,7 @@
         <v>-4.308000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>4.658800000000001</v>
+        <v>4.6588</v>
       </c>
       <c r="O15" t="n">
         <v>-8.9664</v>
@@ -1624,13 +1624,13 @@
         <v>15.5789</v>
       </c>
       <c r="S15" t="n">
-        <v>7.171100000000001</v>
+        <v>7.171099999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2842</v>
+        <v>2.284599999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>4.8865</v>
+        <v>4.8867</v>
       </c>
       <c r="V15" t="n">
         <v>3.7147</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3258</v>
+        <v>4.8474</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1581</v>
+        <v>5.4572</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8323</v>
+        <v>-0.6097</v>
       </c>
       <c r="G16" t="n">
         <v>4.97</v>
@@ -1702,13 +1702,13 @@
         <v>1.5579</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1963</v>
+        <v>-0.6747</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7236</v>
+        <v>-0.4245</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4727</v>
+        <v>-0.2501</v>
       </c>
       <c r="V16" t="n">
         <v>0.9416</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5424</v>
+        <v>1.1878</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4846</v>
+        <v>0.1856</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0579</v>
+        <v>1.0022</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2568</v>
@@ -1780,13 +1780,13 @@
         <v>1.9474</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2844</v>
+        <v>-0.6391</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0683</v>
+        <v>-0.3673</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2162</v>
+        <v>-0.2718</v>
       </c>
       <c r="V17" t="n">
         <v>0.3311</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0626</v>
+        <v>1.1506</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8187</v>
+        <v>-2.6193</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8813</v>
+        <v>3.77</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6798</v>
@@ -1858,13 +1858,13 @@
         <v>2.921</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1992</v>
+        <v>-1.1112</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0327</v>
+        <v>-0.8334</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1665</v>
+        <v>-0.2778</v>
       </c>
       <c r="V18" t="n">
         <v>2.1626</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8919</v>
+        <v>1.0473</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5614</v>
+        <v>0.6611</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3305</v>
+        <v>0.3862</v>
       </c>
       <c r="G19" t="n">
         <v>1.2628</v>
@@ -1936,13 +1936,13 @@
         <v>0.1947</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5656</v>
+        <v>-0.4102</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2907</v>
+        <v>-0.191</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2749</v>
+        <v>-0.2192</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1406</v>
+        <v>-0.0247</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6857</v>
+        <v>-0.4864</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5451</v>
+        <v>0.4616</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4263</v>
@@ -2014,13 +2014,13 @@
         <v>1.1684</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7728</v>
+        <v>-0.6569</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.6045</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0311</v>
+        <v>-0.0524</v>
       </c>
       <c r="V20" t="n">
         <v>0.89</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7167</v>
+        <v>-0.6448</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7664</v>
+        <v>0.8661</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.483</v>
+        <v>-1.5109</v>
       </c>
       <c r="G21" t="n">
         <v>1.2479</v>
@@ -2092,13 +2092,13 @@
         <v>1.3632</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2751</v>
+        <v>-0.2033</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2999</v>
+        <v>-0.2003</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0248</v>
+        <v>-0.003</v>
       </c>
       <c r="V21" t="n">
         <v>-3.0526</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>C. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7032</v>
+        <v>-2.0324</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7813</v>
+        <v>-0.0008</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0781</v>
+        <v>-2.0316</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7613</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2506</v>
+        <v>0.0205</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4893</v>
+        <v>-0.77</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8576</v>
+        <v>0.0611</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7086</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8511</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0963</v>
+        <v>-0.8105</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.542</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6383</v>
+        <v>-0.8105</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3632</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.136</v>
+        <v>-0.0618</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2963</v>
+        <v>-0.0618</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1602</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2726</v>
+        <v>-1.2211</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0516</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>-1.2211</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. VILA DE MIGUEL</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0324</v>
+        <v>-2.2414</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0008</v>
+        <v>-2.0631</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0316</v>
+        <v>-0.1783</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.6545</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0205</v>
+        <v>-2.205</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.77</v>
+        <v>2.8595</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0611</v>
+        <v>-0.6878</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0205</v>
+        <v>-1.9525</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0405</v>
+        <v>1.2647</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8105</v>
+        <v>1.3423</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0.2526</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8105</v>
+        <v>1.5948</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0618</v>
+        <v>-1.3701</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0618</v>
+        <v>-0.6811</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2211</v>
+        <v>-0.9416</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X23" t="n">
         <v>-1.2211</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8187</v>
+        <v>-2.4682</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3621</v>
+        <v>-2.3793</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4566</v>
+        <v>-0.0888</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6545</v>
+        <v>-0.7613</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.205</v>
+        <v>-2.2506</v>
       </c>
       <c r="I24" t="n">
-        <v>2.8595</v>
+        <v>1.4893</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6878</v>
+        <v>-0.8576</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9525</v>
+        <v>-1.7086</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2647</v>
+        <v>0.8511</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3423</v>
+        <v>0.0963</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2526</v>
+        <v>-0.542</v>
       </c>
       <c r="O24" t="n">
-        <v>1.5948</v>
+        <v>0.6383</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9737</v>
+        <v>-1.1684</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3895</v>
+        <v>1.3632</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9474</v>
+        <v>-0.629</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9801</v>
+        <v>-0.3018</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.3272</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9416</v>
+        <v>-1.2726</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2795</v>
+        <v>-0.0516</v>
       </c>
       <c r="X24" t="n">
         <v>-1.2211</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9808</v>
+        <v>-3.1245</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8095</v>
+        <v>-2.0089</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1713</v>
+        <v>-1.1157</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6206</v>
@@ -2404,13 +2404,13 @@
         <v>1.7526</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3339</v>
+        <v>-0.4776</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.192</v>
+        <v>-0.3913</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.142</v>
+        <v>-0.0863</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8316</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.0635</v>
+        <v>-4.0867</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.4979</v>
+        <v>-5.2985</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4344</v>
+        <v>1.2118</v>
       </c>
       <c r="G26" t="n">
         <v>-1.6076</v>
@@ -2482,13 +2482,13 @@
         <v>0.9737</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5933</v>
+        <v>-0.6165</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7946</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2014</v>
+        <v>-0.0212</v>
       </c>
       <c r="V26" t="n">
         <v>0.2795</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.0553</v>
+        <v>-5.2987</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.4359</v>
+        <v>-4.7349</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5638</v>
       </c>
       <c r="G27" t="n">
         <v>-2.8359</v>
@@ -2560,13 +2560,13 @@
         <v>1.9474</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.3207</v>
       </c>
       <c r="T27" t="n">
-        <v>0.0646</v>
+        <v>-0.2344</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.142</v>
+        <v>-0.0863</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-11.6885</v>
+        <v>-11.6883</v>
       </c>
       <c r="E28" t="n">
-        <v>-12.4214</v>
+        <v>-12.4212</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7330000000000002</v>
+        <v>0.7330000000000004</v>
       </c>
       <c r="G28" t="n">
         <v>-0.8026000000000004</v>
@@ -2611,7 +2611,7 @@
         <v>11.395</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3079</v>
+        <v>4.307900000000001</v>
       </c>
       <c r="K28" t="n">
         <v>-4.6585</v>
@@ -2620,7 +2620,7 @@
         <v>8.966599999999998</v>
       </c>
       <c r="M28" t="n">
-        <v>-5.1103</v>
+        <v>-5.110300000000001</v>
       </c>
       <c r="N28" t="n">
         <v>-7.5391</v>
@@ -2638,19 +2638,19 @@
         <v>15.579</v>
       </c>
       <c r="S28" t="n">
-        <v>-7.1711</v>
+        <v>-7.171099999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>-4.886699999999999</v>
+        <v>-4.8867</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.2844</v>
+        <v>-2.2843</v>
       </c>
       <c r="V28" t="n">
         <v>-3.7147</v>
       </c>
       <c r="W28" t="n">
-        <v>3.736400000000001</v>
+        <v>3.7364</v>
       </c>
       <c r="X28" t="n">
         <v>-7.4512</v>
